--- a/data/tony/excel/800537954_2026_invoices.xlsx
+++ b/data/tony/excel/800537954_2026_invoices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,122 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>Α/Α</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>400012360709395</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>094420307</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ΤΕΣΑΕ ΕΠΙΧΕΙΡΗΣΕΙΣ ΣΧΕΔΙΑΣΗΣ ΑΝΑΠΤΥΞΗΣ ΕΦΑΡΜΟΓΩΝ ΠΛΗΡΟΦΟΡΙΚΗ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ΤΠΥ-Ε</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>62644</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>22/01/2026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Τιμολόγιο Παροχής Υπηρεσιών</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>180,00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>43,20</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>223,20</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>62644</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>400012335783676</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>094420307</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ΤΕΣΑΕ ΕΠΙΧΕΙΡΗΣΕΙΣ ΣΧΕΔΙΑΣΗΣ ΑΝΑΠΤΥΞΗΣ ΕΦΑΡΜΟΓΩΝ ΠΛΗΡΟΦΟΡΙΚΗ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ΤΠΥ-Ε</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>62431</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>20/01/2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Τιμολόγιο Παροχής Υπηρεσιών</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>159,00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>38,16</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>197,16</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>62431</t>
         </is>
       </c>
     </row>
